--- a/NimapInfotech_TestCases.xlsx
+++ b/NimapInfotech_TestCases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jatin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0F7CB3-11A7-476F-B8A0-2C6F532A8AA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A7126E-1ADB-4AD9-92AB-8964C2D4861C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sign Up" sheetId="2" r:id="rId1"/>
@@ -242,9 +242,6 @@
     <t>Sign Up</t>
   </si>
   <si>
-    <t>No check on weak passwords</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -293,9 +290,6 @@
     <t>BUG07</t>
   </si>
   <si>
-    <t>"No validation for mail &amp; password has linked to the other account</t>
-  </si>
-  <si>
     <t>No validation using contact number</t>
   </si>
   <si>
@@ -303,6 +297,12 @@
   </si>
   <si>
     <t>Error msg should be display</t>
+  </si>
+  <si>
+    <t>No validation for mail &amp; password has linked to the other account</t>
+  </si>
+  <si>
+    <t>No validation on character special character should be used</t>
   </si>
 </sst>
 </file>
@@ -1002,13 +1002,13 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -1048,7 +1048,7 @@
         <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1068,7 +1068,7 @@
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1234,115 +1234,115 @@
         <v>71</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" t="s">
         <v>72</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" t="s">
         <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" t="s">
         <v>76</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>77</v>
       </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" t="s">
         <v>80</v>
       </c>
-      <c r="C8" t="s">
-        <v>81</v>
-      </c>
       <c r="D8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" t="s">
         <v>73</v>
-      </c>
-      <c r="E8" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
